--- a/TEGR_10x10_Matrix_WORKING.xlsx
+++ b/TEGR_10x10_Matrix_WORKING.xlsx
@@ -1530,14 +1530,14 @@
         <v>0</v>
       </c>
       <c r="Q13" s="29">
-        <f>C14*C28^2/C29</f>
+        <f>C28^2/(C14*C29)</f>
         <v/>
       </c>
       <c r="R13" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S13" s="29">
-        <f>C12*C28^2/C29</f>
+        <f>-C12*C28^2/(C14^2*C29)</f>
         <v/>
       </c>
       <c r="T13" s="1" t="n"/>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="G45" s="30">
-        <f>C14*C12*C28^2/C29</f>
+        <f>(C12/C14)*C28^2/C29</f>
         <v/>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="C92" s="34">
-        <f>MOD(C13+C75*C12*C28^2/C29*C30, 2*PI())</f>
+        <f>MOD(C13+(C12/C75)*C28^2/C29*C30, 2*PI())</f>
         <v/>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -4105,7 +4105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:S92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4400,6 +4400,8 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
+    <row r="92"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4412,7 +4414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:S92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4434,7 +4436,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -4491,7 +4492,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -4553,7 +4553,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -4609,6 +4608,8 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
+    <row r="92"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
